--- a/grupos/6ASV - Estadisticos 20222.xlsx
+++ b/grupos/6ASV - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="73">
   <si>
     <t>Materia</t>
   </si>
@@ -150,12 +149,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Polanco Domínguez Rosa María</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Polanco Domínguez Rosa María</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -180,166 +179,73 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>COCOTLE</t>
+    <t>VAZQUEZ</t>
   </si>
   <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GAMEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>IBAÑEZ</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>MAYA</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>TLAXCALA</t>
+    <t>TZIZIHUA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>SILVERIO</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
     <t>SOLIS</t>
   </si>
   <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO SAID</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>SURISADAY</t>
+    <t>DORA LUZ</t>
   </si>
   <si>
     <t>MARCOS</t>
   </si>
   <si>
-    <t>JESUS SAMUEL</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>ARIZBETH</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
     <t>EMMANUEL</t>
   </si>
   <si>
     <t>JESUS ANTONIO</t>
   </si>
   <si>
-    <t>FRANCISCO YAEL</t>
-  </si>
-  <si>
     <t>VICTOR HUGO</t>
   </si>
   <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
     <t>MICHELLE ROBERTA</t>
   </si>
   <si>
-    <t>JESUS JOAN</t>
-  </si>
-  <si>
     <t>JOSE MANUEL</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -392,11 +298,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -837,13 +744,13 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -852,7 +759,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -873,7 +780,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -888,7 +795,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -914,13 +821,13 @@
         <v>5</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -929,7 +836,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -953,10 +860,10 @@
         <v>5</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>6</v>
@@ -991,13 +898,13 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1006,7 +913,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1027,7 +934,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1068,13 +975,13 @@
         <v>4</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1083,7 +990,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1104,7 +1011,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -1145,13 +1052,13 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1160,7 +1067,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1181,10 +1088,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1222,13 +1129,13 @@
         <v>4</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -1237,7 +1144,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1258,10 +1165,10 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1299,13 +1206,13 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1314,7 +1221,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1335,7 +1242,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1376,13 +1283,13 @@
         <v>6</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1391,7 +1298,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1412,7 +1319,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
         <v>6</v>
@@ -1427,7 +1334,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1453,13 +1360,13 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -1468,7 +1375,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1489,7 +1396,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -1504,7 +1411,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1530,13 +1437,13 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -1545,7 +1452,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1566,13 +1473,13 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>6</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1607,13 +1514,13 @@
         <v>4</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1622,7 +1529,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1643,10 +1550,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1684,13 +1591,13 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1699,7 +1606,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1720,7 +1627,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1761,13 +1668,13 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1776,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1797,13 +1704,13 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1812,7 +1719,7 @@
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1838,13 +1745,13 @@
         <v>4</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1853,7 +1760,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1880,7 +1787,7 @@
         <v>5</v>
       </c>
       <c r="V17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W17">
         <v>8</v>
@@ -1915,13 +1822,13 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -1930,7 +1837,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1951,13 +1858,13 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -1966,7 +1873,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1992,13 +1899,13 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -2007,7 +1914,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2031,7 +1938,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>9</v>
@@ -2069,13 +1976,13 @@
         <v>5</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2084,7 +1991,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2146,13 +2053,13 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2161,7 +2068,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2182,10 +2089,10 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2197,7 +2104,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2223,13 +2130,13 @@
         <v>4</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2238,7 +2145,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2259,7 +2166,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2410,13 +2317,13 @@
         <v>92</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -2425,7 +2332,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -2469,13 +2376,13 @@
         <v>92</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -2484,7 +2391,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -2528,13 +2435,13 @@
         <v>92</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -2543,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -2587,13 +2494,13 @@
         <v>76</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -2602,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -2646,13 +2553,13 @@
         <v>92</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -2661,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -2705,13 +2612,13 @@
         <v>92</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -2720,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -2764,13 +2671,13 @@
         <v>92</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2779,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -2823,13 +2730,13 @@
         <v>92</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2838,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -2882,13 +2789,13 @@
         <v>92</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -2897,7 +2804,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -2941,13 +2848,13 @@
         <v>92</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -2956,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -3000,13 +2907,13 @@
         <v>76</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -3015,7 +2922,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -3059,13 +2966,13 @@
         <v>92</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -3074,7 +2981,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3118,13 +3025,13 @@
         <v>92</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -3133,7 +3040,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3177,13 +3084,13 @@
         <v>80</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>76.7</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -3192,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -3236,13 +3143,13 @@
         <v>92</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -3251,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -3295,13 +3202,13 @@
         <v>92</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>116</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -3310,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -3354,13 +3261,13 @@
         <v>92</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -3369,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -3413,13 +3320,13 @@
         <v>92</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -3428,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -3472,13 +3379,13 @@
         <v>76</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>63.3</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>112</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -3487,7 +3394,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -3524,6 +3431,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -3560,7 +3469,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>43</v>
@@ -3574,25 +3483,25 @@
       <c r="E2">
         <v>8</v>
       </c>
-      <c r="F2">
-        <v>57.89</v>
-      </c>
-      <c r="G2">
-        <v>42.11</v>
+      <c r="F2" s="2">
+        <v>57.9</v>
+      </c>
+      <c r="G2" s="2">
+        <v>42.1</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
@@ -3601,24 +3510,24 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>4</v>
-      </c>
-      <c r="F3">
-        <v>78.95</v>
-      </c>
-      <c r="G3">
-        <v>21.05</v>
+        <v>8</v>
+      </c>
+      <c r="F3" s="2">
+        <v>57.9</v>
+      </c>
+      <c r="G3" s="2">
+        <v>42.1</v>
       </c>
       <c r="H3">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3633,24 +3542,24 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>4</v>
-      </c>
-      <c r="F4">
-        <v>78.95</v>
-      </c>
-      <c r="G4">
-        <v>21.05</v>
+        <v>3</v>
+      </c>
+      <c r="F4" s="2">
+        <v>84.2</v>
+      </c>
+      <c r="G4" s="2">
+        <v>15.8</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3670,11 +3579,11 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5">
-        <v>89.47</v>
-      </c>
-      <c r="G5">
-        <v>10.53</v>
+      <c r="F5" s="2">
+        <v>89.5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10.5</v>
       </c>
       <c r="H5">
         <v>7.3</v>
@@ -3682,7 +3591,7 @@
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3702,10 +3611,10 @@
       <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>100</v>
-      </c>
-      <c r="G6">
+      <c r="F6" s="2">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6">
@@ -3714,7 +3623,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3734,19 +3643,19 @@
       <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7">
-        <v>100</v>
-      </c>
-      <c r="G7">
+      <c r="F7" s="2">
+        <v>100</v>
+      </c>
+      <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3791,361 +3700,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20330051920317</v>
-      </c>
-      <c r="B2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>20330051920318</v>
-      </c>
-      <c r="B3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>20330051920320</v>
-      </c>
-      <c r="B4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>20330051920321</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>20330051920322</v>
-      </c>
-      <c r="B6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>20330051920323</v>
-      </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>20330051920380</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" t="s">
-        <v>92</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>20330051920324</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D9" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>20330051920325</v>
-      </c>
-      <c r="B10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C10" t="s">
-        <v>78</v>
-      </c>
-      <c r="D10" t="s">
-        <v>94</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>20330051920397</v>
-      </c>
-      <c r="B11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>20330051920326</v>
-      </c>
-      <c r="B12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>20330051920327</v>
-      </c>
-      <c r="B13" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>20330051920396</v>
-      </c>
-      <c r="B14" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>20330051920329</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>20330051920330</v>
-      </c>
-      <c r="B16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C16" t="s">
-        <v>82</v>
-      </c>
-      <c r="D16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>20330051920331</v>
-      </c>
-      <c r="B17" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>19330051920408</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>20330051920333</v>
-      </c>
-      <c r="B19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" t="s">
-        <v>84</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>20330051920335</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" t="s">
-        <v>104</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4177,22 +3732,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920317</v>
+        <v>20330051920335</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4200,22 +3755,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920317</v>
+        <v>20330051920335</v>
       </c>
       <c r="B3" t="s">
         <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -4226,19 +3781,19 @@
         <v>20330051920322</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4246,22 +3801,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920322</v>
+        <v>20330051920397</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4272,19 +3827,19 @@
         <v>20330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4292,19 +3847,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920326</v>
+        <v>20330051920396</v>
       </c>
       <c r="B7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" t="s">
         <v>62</v>
       </c>
-      <c r="C7" t="s">
-        <v>80</v>
-      </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
@@ -4315,22 +3870,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920335</v>
+        <v>20330051920331</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4338,47 +3893,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920335</v>
+        <v>20330051920333</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>43</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920397</v>
-      </c>
-      <c r="B10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>43</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ASV - Estadisticos 20222.xlsx
+++ b/grupos/6ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
   <si>
     <t>Materia</t>
   </si>
@@ -155,12 +155,12 @@
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
@@ -179,9 +179,6 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -200,9 +197,6 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -216,9 +210,6 @@
   </si>
   <si>
     <t>SOLIS</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
   </si>
   <si>
     <t>MARCOS</t>
@@ -753,10 +744,10 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>10</v>
@@ -830,10 +821,10 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>5</v>
@@ -866,10 +857,10 @@
         <v>8</v>
       </c>
       <c r="W5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y5">
         <v>5</v>
@@ -907,10 +898,10 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -984,10 +975,10 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>4</v>
@@ -1023,7 +1014,7 @@
         <v>5</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y7">
         <v>5</v>
@@ -1061,10 +1052,10 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1097,10 +1088,10 @@
         <v>9</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1138,10 +1129,10 @@
         <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>5</v>
@@ -1174,7 +1165,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1215,10 +1206,10 @@
         <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>10</v>
@@ -1292,10 +1283,10 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M11">
         <v>8</v>
@@ -1369,10 +1360,10 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
         <v>10</v>
@@ -1446,10 +1437,10 @@
         <v>10</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>5</v>
@@ -1485,7 +1476,7 @@
         <v>6</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1523,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>5</v>
@@ -1559,10 +1550,10 @@
         <v>8</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>5</v>
@@ -1600,10 +1591,10 @@
         <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>6</v>
@@ -1636,10 +1627,10 @@
         <v>10</v>
       </c>
       <c r="W15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -1677,10 +1668,10 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>7</v>
@@ -1713,7 +1704,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -1754,10 +1745,10 @@
         <v>10</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>5</v>
@@ -1790,7 +1781,7 @@
         <v>8</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -1831,10 +1822,10 @@
         <v>10</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>7</v>
@@ -1867,10 +1858,10 @@
         <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -1908,10 +1899,10 @@
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>8</v>
@@ -1944,7 +1935,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -1985,10 +1976,10 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>5</v>
@@ -2062,10 +2053,10 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>7</v>
@@ -2098,7 +2089,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2139,10 +2130,10 @@
         <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>4</v>
@@ -2175,10 +2166,10 @@
         <v>6</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2326,10 +2317,10 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M4">
         <v>104</v>
@@ -2385,10 +2376,10 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>80</v>
@@ -2444,10 +2435,10 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M6">
         <v>84</v>
@@ -2503,10 +2494,10 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M7">
         <v>84</v>
@@ -2562,10 +2553,10 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M8">
         <v>104</v>
@@ -2621,10 +2612,10 @@
         <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M9">
         <v>100</v>
@@ -2680,10 +2671,10 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M10">
         <v>104</v>
@@ -2739,10 +2730,10 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="M11">
         <v>104</v>
@@ -2798,10 +2789,10 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M12">
         <v>104</v>
@@ -2857,10 +2848,10 @@
         <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -2916,10 +2907,10 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M14">
         <v>100</v>
@@ -2975,10 +2966,10 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M15">
         <v>104</v>
@@ -3034,10 +3025,10 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -3093,10 +3084,10 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M17">
         <v>80</v>
@@ -3152,10 +3143,10 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M18">
         <v>104</v>
@@ -3211,10 +3202,10 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M19">
         <v>104</v>
@@ -3270,10 +3261,10 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M20">
         <v>92</v>
@@ -3329,10 +3320,10 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="M21">
         <v>100</v>
@@ -3388,10 +3379,10 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="M22">
         <v>84</v>
@@ -3533,7 +3524,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>45</v>
@@ -3542,16 +3533,16 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2">
-        <v>84.2</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>15.8</v>
+        <v>21.1</v>
       </c>
       <c r="H4">
         <v>7.1</v>
@@ -3565,7 +3556,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
@@ -3574,19 +3565,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>89.5</v>
+        <v>84.2</v>
       </c>
       <c r="G5" s="2">
-        <v>10.5</v>
+        <v>15.8</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3606,19 +3597,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>100</v>
+        <v>89.5</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3700,7 +3691,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3732,22 +3723,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920335</v>
+        <v>20330051920322</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3755,16 +3746,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920335</v>
+        <v>20330051920397</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" t="s">
         <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -3778,16 +3769,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920322</v>
+        <v>20330051920326</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
         <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -3801,22 +3792,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920397</v>
+        <v>20330051920396</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -3824,22 +3815,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920326</v>
+        <v>20330051920331</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -3847,16 +3838,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920396</v>
+        <v>20330051920333</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -3865,52 +3856,6 @@
         <v>43</v>
       </c>
       <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920331</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920333</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" t="s">
-        <v>72</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ASV - Estadisticos 20222.xlsx
+++ b/grupos/6ASV - Estadisticos 20222.xlsx
@@ -2293,25 +2293,25 @@
         <v>80</v>
       </c>
       <c r="C4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D4">
         <v>100</v>
       </c>
       <c r="E4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F4">
-        <v>104</v>
+        <v>86.7</v>
       </c>
       <c r="G4">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J4">
         <v>100</v>
@@ -2320,28 +2320,28 @@
         <v>100</v>
       </c>
       <c r="L4">
-        <v>96</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M4">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -2352,55 +2352,55 @@
         <v>60</v>
       </c>
       <c r="C5">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="D5">
         <v>100</v>
       </c>
       <c r="E5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F5">
-        <v>92</v>
+        <v>76.7</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>73.3</v>
+        <v>66.7</v>
       </c>
       <c r="I5">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="J5">
         <v>100</v>
       </c>
       <c r="K5">
-        <v>84</v>
+        <v>92.7</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>87.3</v>
       </c>
       <c r="M5">
-        <v>80</v>
+        <v>87.8</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>87.3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2411,25 +2411,25 @@
         <v>90</v>
       </c>
       <c r="C6">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D6">
         <v>100</v>
       </c>
       <c r="E6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F6">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="G6">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="I6">
-        <v>112</v>
+        <v>91.7</v>
       </c>
       <c r="J6">
         <v>100</v>
@@ -2438,28 +2438,28 @@
         <v>100</v>
       </c>
       <c r="L6">
-        <v>96</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M6">
-        <v>84</v>
+        <v>89.8</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2470,55 +2470,55 @@
         <v>80</v>
       </c>
       <c r="C7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D7">
         <v>100</v>
       </c>
       <c r="E7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F7">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="G7">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H7">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="I7">
-        <v>112</v>
+        <v>96.7</v>
       </c>
       <c r="J7">
         <v>100</v>
       </c>
       <c r="K7">
-        <v>72</v>
+        <v>87.3</v>
       </c>
       <c r="L7">
-        <v>88</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M7">
-        <v>84</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>87.3</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2529,25 +2529,25 @@
         <v>90</v>
       </c>
       <c r="C8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D8">
         <v>100</v>
       </c>
       <c r="E8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G8">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>90</v>
       </c>
       <c r="I8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J8">
         <v>100</v>
@@ -2556,28 +2556,28 @@
         <v>100</v>
       </c>
       <c r="L8">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="M8">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -2588,25 +2588,25 @@
         <v>80</v>
       </c>
       <c r="C9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D9">
         <v>100</v>
       </c>
       <c r="E9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F9">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I9">
-        <v>116</v>
+        <v>98.3</v>
       </c>
       <c r="J9">
         <v>100</v>
@@ -2615,28 +2615,28 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2647,25 +2647,25 @@
         <v>100</v>
       </c>
       <c r="C10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D10">
         <v>100</v>
       </c>
       <c r="E10">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F10">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="G10">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H10">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I10">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J10">
         <v>100</v>
@@ -2674,28 +2674,28 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>96</v>
+        <v>92.7</v>
       </c>
       <c r="M10">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -2706,25 +2706,25 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D11">
         <v>100</v>
       </c>
       <c r="E11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F11">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="G11">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="I11">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J11">
         <v>100</v>
@@ -2733,28 +2733,28 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>84</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M11">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -2765,25 +2765,25 @@
         <v>80</v>
       </c>
       <c r="C12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D12">
         <v>100</v>
       </c>
       <c r="E12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G12">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H12">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="I12">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J12">
         <v>100</v>
@@ -2795,25 +2795,25 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -2824,25 +2824,25 @@
         <v>90</v>
       </c>
       <c r="C13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D13">
         <v>100</v>
       </c>
       <c r="E13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F13">
-        <v>100</v>
+        <v>83.3</v>
       </c>
       <c r="G13">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H13">
         <v>90</v>
       </c>
       <c r="I13">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J13">
         <v>100</v>
@@ -2851,28 +2851,28 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>96</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2883,25 +2883,25 @@
         <v>80</v>
       </c>
       <c r="C14">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="D14">
         <v>100</v>
       </c>
       <c r="E14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F14">
-        <v>116</v>
+        <v>96.7</v>
       </c>
       <c r="G14">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H14">
         <v>80</v>
       </c>
       <c r="I14">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="J14">
         <v>100</v>
@@ -2910,28 +2910,28 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>96</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>89.8</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2942,55 +2942,55 @@
         <v>90</v>
       </c>
       <c r="C15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D15">
         <v>100</v>
       </c>
       <c r="E15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G15">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H15">
         <v>90</v>
       </c>
       <c r="I15">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>92</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L15">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="M15">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3001,25 +3001,25 @@
         <v>90</v>
       </c>
       <c r="C16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D16">
         <v>100</v>
       </c>
       <c r="E16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G16">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H16">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="I16">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J16">
         <v>100</v>
@@ -3028,28 +3028,28 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>92</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>91.7</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3060,55 +3060,55 @@
         <v>70</v>
       </c>
       <c r="C17">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="D17">
         <v>100</v>
       </c>
       <c r="E17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G17">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="H17">
-        <v>76.7</v>
+        <v>73.3</v>
       </c>
       <c r="I17">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>92</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L17">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="M17">
-        <v>80</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3119,55 +3119,55 @@
         <v>80</v>
       </c>
       <c r="C18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D18">
         <v>100</v>
       </c>
       <c r="E18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G18">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>83.3</v>
+        <v>81.7</v>
       </c>
       <c r="I18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J18">
         <v>100</v>
       </c>
       <c r="K18">
-        <v>92</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L18">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="M18">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -3178,25 +3178,25 @@
         <v>90</v>
       </c>
       <c r="C19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D19">
         <v>100</v>
       </c>
       <c r="E19">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F19">
-        <v>112</v>
+        <v>93.3</v>
       </c>
       <c r="G19">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="I19">
-        <v>116</v>
+        <v>98.3</v>
       </c>
       <c r="J19">
         <v>100</v>
@@ -3205,28 +3205,28 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>92</v>
+        <v>92.7</v>
       </c>
       <c r="M19">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>98.3</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -3237,55 +3237,55 @@
         <v>90</v>
       </c>
       <c r="C20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D20">
         <v>100</v>
       </c>
       <c r="E20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F20">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G20">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H20">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="I20">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="L20">
-        <v>92</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="M20">
-        <v>92</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>93.90000000000001</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3296,55 +3296,55 @@
         <v>70</v>
       </c>
       <c r="C21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D21">
         <v>100</v>
       </c>
       <c r="E21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G21">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="H21">
-        <v>93.3</v>
+        <v>81.7</v>
       </c>
       <c r="I21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>92</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="L21">
-        <v>96</v>
+        <v>98.2</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>98.2</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3355,55 +3355,55 @@
         <v>100</v>
       </c>
       <c r="C22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="D22">
         <v>100</v>
       </c>
       <c r="E22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F22">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G22">
-        <v>76</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H22">
-        <v>63.3</v>
+        <v>81.7</v>
       </c>
       <c r="I22">
-        <v>112</v>
+        <v>96.7</v>
       </c>
       <c r="J22">
         <v>100</v>
       </c>
       <c r="K22">
-        <v>76</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L22">
-        <v>88</v>
+        <v>94.5</v>
       </c>
       <c r="M22">
-        <v>84</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>81.7</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>94.5</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/6ASV - Estadisticos 20222.xlsx
+++ b/grupos/6ASV - Estadisticos 20222.xlsx
@@ -2308,7 +2308,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -2326,7 +2326,7 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -2367,7 +2367,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="I5">
         <v>93.3</v>
@@ -2385,7 +2385,7 @@
         <v>87.8</v>
       </c>
       <c r="N5">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="O5">
         <v>93.3</v>
@@ -2426,7 +2426,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="I6">
         <v>91.7</v>
@@ -2444,7 +2444,7 @@
         <v>89.8</v>
       </c>
       <c r="N6">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="O6">
         <v>91.7</v>
@@ -2485,7 +2485,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="H7">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="I7">
         <v>96.7</v>
@@ -2503,7 +2503,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N7">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="O7">
         <v>96.7</v>
@@ -2544,7 +2544,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -2562,7 +2562,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -2603,7 +2603,7 @@
         <v>100</v>
       </c>
       <c r="H9">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I9">
         <v>98.3</v>
@@ -2621,7 +2621,7 @@
         <v>98</v>
       </c>
       <c r="N9">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O9">
         <v>98.3</v>
@@ -2662,7 +2662,7 @@
         <v>100</v>
       </c>
       <c r="H10">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="I10">
         <v>95</v>
@@ -2680,7 +2680,7 @@
         <v>100</v>
       </c>
       <c r="N10">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="O10">
         <v>95</v>
@@ -2721,7 +2721,7 @@
         <v>100</v>
       </c>
       <c r="H11">
-        <v>93.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="I11">
         <v>100</v>
@@ -2739,7 +2739,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>93.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -2780,7 +2780,7 @@
         <v>100</v>
       </c>
       <c r="H12">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="I12">
         <v>100</v>
@@ -2798,7 +2798,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -2839,7 +2839,7 @@
         <v>100</v>
       </c>
       <c r="H13">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I13">
         <v>100</v>
@@ -2857,7 +2857,7 @@
         <v>98</v>
       </c>
       <c r="N13">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O13">
         <v>100</v>
@@ -2898,7 +2898,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="H14">
-        <v>80</v>
+        <v>82.8</v>
       </c>
       <c r="I14">
         <v>95</v>
@@ -2916,7 +2916,7 @@
         <v>89.8</v>
       </c>
       <c r="N14">
-        <v>80</v>
+        <v>82.8</v>
       </c>
       <c r="O14">
         <v>95</v>
@@ -2957,7 +2957,7 @@
         <v>100</v>
       </c>
       <c r="H15">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="I15">
         <v>100</v>
@@ -2975,7 +2975,7 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>90</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="O15">
         <v>100</v>
@@ -3016,7 +3016,7 @@
         <v>100</v>
       </c>
       <c r="H16">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="I16">
         <v>100</v>
@@ -3034,7 +3034,7 @@
         <v>98</v>
       </c>
       <c r="N16">
-        <v>91.7</v>
+        <v>94.8</v>
       </c>
       <c r="O16">
         <v>100</v>
@@ -3075,7 +3075,7 @@
         <v>87</v>
       </c>
       <c r="H17">
-        <v>73.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I17">
         <v>90</v>
@@ -3093,7 +3093,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N17">
-        <v>73.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="O17">
         <v>90</v>
@@ -3134,7 +3134,7 @@
         <v>100</v>
       </c>
       <c r="H18">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -3152,7 +3152,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -3193,7 +3193,7 @@
         <v>100</v>
       </c>
       <c r="H19">
-        <v>95</v>
+        <v>98.3</v>
       </c>
       <c r="I19">
         <v>98.3</v>
@@ -3211,7 +3211,7 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>95</v>
+        <v>98.3</v>
       </c>
       <c r="O19">
         <v>98.3</v>
@@ -3252,7 +3252,7 @@
         <v>100</v>
       </c>
       <c r="H20">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I20">
         <v>95</v>
@@ -3270,7 +3270,7 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N20">
-        <v>85</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="O20">
         <v>95</v>
@@ -3311,7 +3311,7 @@
         <v>100</v>
       </c>
       <c r="H21">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="I21">
         <v>100</v>
@@ -3329,7 +3329,7 @@
         <v>98</v>
       </c>
       <c r="N21">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -3370,7 +3370,7 @@
         <v>82.59999999999999</v>
       </c>
       <c r="H22">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="I22">
         <v>96.7</v>
@@ -3388,7 +3388,7 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N22">
-        <v>81.7</v>
+        <v>84.5</v>
       </c>
       <c r="O22">
         <v>96.7</v>

--- a/grupos/6ASV - Estadisticos 20222.xlsx
+++ b/grupos/6ASV - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="68">
   <si>
     <t>Materia</t>
   </si>
@@ -149,21 +149,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
     <t>Castillo Cruz Carlos Samuel</t>
   </si>
   <si>
@@ -179,7 +179,7 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>GARCIA</t>
+    <t>APALE</t>
   </si>
   <si>
     <t>IBAÑEZ</t>
@@ -188,16 +188,13 @@
     <t>LUNA</t>
   </si>
   <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
@@ -206,13 +203,13 @@
     <t>MORALES</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>EMMANUEL</t>
@@ -221,13 +218,10 @@
     <t>JESUS ANTONIO</t>
   </si>
   <si>
-    <t>VICTOR HUGO</t>
-  </si>
-  <si>
-    <t>MICHELLE ROBERTA</t>
-  </si>
-  <si>
-    <t>JOSE MANUEL</t>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>JESUS JOAN</t>
   </si>
 </sst>
 </file>
@@ -753,25 +747,25 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>9</v>
@@ -830,40 +824,40 @@
         <v>5</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>5</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
       </c>
       <c r="Y5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -907,40 +901,40 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>7</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>9</v>
       </c>
       <c r="W6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -984,22 +978,22 @@
         <v>4</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T7">
         <v>5</v>
@@ -1061,22 +1055,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1138,31 +1132,31 @@
         <v>5</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
         <v>6</v>
       </c>
       <c r="U9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1171,7 +1165,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1215,22 +1209,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1292,22 +1286,22 @@
         <v>8</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1369,28 +1363,28 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>10</v>
@@ -1399,10 +1393,10 @@
         <v>7</v>
       </c>
       <c r="X12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1446,25 +1440,25 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1523,31 +1517,31 @@
         <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>6</v>
@@ -1600,34 +1594,34 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>8</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>10</v>
       </c>
       <c r="W15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X15">
         <v>7</v>
@@ -1677,40 +1671,40 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>7</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1754,37 +1748,37 @@
         <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>5</v>
@@ -1831,31 +1825,31 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>8</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -1864,7 +1858,7 @@
         <v>7</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1908,34 +1902,34 @@
         <v>8</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -1985,37 +1979,37 @@
         <v>5</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2062,28 +2056,28 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21">
         <v>10</v>
@@ -2092,10 +2086,10 @@
         <v>7</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2139,25 +2133,25 @@
         <v>4</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2169,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2326,10 +2320,10 @@
         <v>100</v>
       </c>
       <c r="N4">
-        <v>93.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="O4">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P4">
         <v>100</v>
@@ -2338,7 +2332,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>90.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -2385,22 +2379,22 @@
         <v>87.8</v>
       </c>
       <c r="N5">
-        <v>69</v>
+        <v>46.8</v>
       </c>
       <c r="O5">
-        <v>93.3</v>
+        <v>80</v>
       </c>
       <c r="P5">
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>92.7</v>
+        <v>86.3</v>
       </c>
       <c r="R5">
-        <v>87.3</v>
+        <v>68.8</v>
       </c>
       <c r="S5">
-        <v>87.8</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -2444,10 +2438,10 @@
         <v>89.8</v>
       </c>
       <c r="N6">
-        <v>94.8</v>
+        <v>95.7</v>
       </c>
       <c r="O6">
-        <v>91.7</v>
+        <v>92.2</v>
       </c>
       <c r="P6">
         <v>100</v>
@@ -2456,10 +2450,10 @@
         <v>100</v>
       </c>
       <c r="R6">
-        <v>96.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S6">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -2503,22 +2497,22 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N7">
-        <v>84.5</v>
+        <v>70.2</v>
       </c>
       <c r="O7">
-        <v>96.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="P7">
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>87.3</v>
+        <v>72.5</v>
       </c>
       <c r="R7">
-        <v>90.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="S7">
-        <v>81.59999999999999</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -2562,7 +2556,7 @@
         <v>100</v>
       </c>
       <c r="N8">
-        <v>93.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -2574,7 +2568,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>98.2</v>
+        <v>98.7</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -2621,10 +2615,10 @@
         <v>98</v>
       </c>
       <c r="N9">
-        <v>87.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="O9">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -2633,10 +2627,10 @@
         <v>100</v>
       </c>
       <c r="R9">
-        <v>98.2</v>
+        <v>98.7</v>
       </c>
       <c r="S9">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -2683,7 +2677,7 @@
         <v>100</v>
       </c>
       <c r="O10">
-        <v>95</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="P10">
         <v>100</v>
@@ -2692,7 +2686,7 @@
         <v>100</v>
       </c>
       <c r="R10">
-        <v>92.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -2739,7 +2733,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>96.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="O11">
         <v>100</v>
@@ -2748,10 +2742,10 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R11">
-        <v>89.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -2798,7 +2792,7 @@
         <v>100</v>
       </c>
       <c r="N12">
-        <v>84.5</v>
+        <v>86.2</v>
       </c>
       <c r="O12">
         <v>100</v>
@@ -2807,7 +2801,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -2857,22 +2851,22 @@
         <v>98</v>
       </c>
       <c r="N13">
-        <v>93.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="O13">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="R13">
-        <v>89.09999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S13">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -2916,22 +2910,22 @@
         <v>89.8</v>
       </c>
       <c r="N14">
-        <v>82.8</v>
+        <v>83</v>
       </c>
       <c r="O14">
-        <v>95</v>
+        <v>93.3</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="R14">
-        <v>96.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="S14">
-        <v>89.8</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -2975,19 +2969,19 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>93.09999999999999</v>
+        <v>95.7</v>
       </c>
       <c r="O15">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="R15">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -3034,22 +3028,22 @@
         <v>98</v>
       </c>
       <c r="N16">
-        <v>94.8</v>
+        <v>95.7</v>
       </c>
       <c r="O16">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R16">
-        <v>96.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S16">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3093,22 +3087,22 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N17">
-        <v>75.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="O17">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>96.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="R17">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -3152,7 +3146,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>84.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -3161,10 +3155,10 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>96.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R18">
-        <v>98.2</v>
+        <v>98.7</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -3211,19 +3205,19 @@
         <v>100</v>
       </c>
       <c r="N19">
-        <v>98.3</v>
+        <v>95.7</v>
       </c>
       <c r="O19">
-        <v>98.3</v>
+        <v>97.8</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="R19">
-        <v>92.7</v>
+        <v>94.8</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -3270,22 +3264,22 @@
         <v>93.90000000000001</v>
       </c>
       <c r="N20">
-        <v>87.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="O20">
-        <v>95</v>
+        <v>86.7</v>
       </c>
       <c r="P20">
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>98.2</v>
+        <v>96.3</v>
       </c>
       <c r="R20">
-        <v>96.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="S20">
-        <v>93.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -3329,22 +3323,22 @@
         <v>98</v>
       </c>
       <c r="N21">
-        <v>84.5</v>
+        <v>87.2</v>
       </c>
       <c r="O21">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>96.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="R21">
-        <v>98.2</v>
+        <v>98.7</v>
       </c>
       <c r="S21">
-        <v>98</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -3388,22 +3382,22 @@
         <v>81.59999999999999</v>
       </c>
       <c r="N22">
-        <v>84.5</v>
+        <v>70.2</v>
       </c>
       <c r="O22">
-        <v>96.7</v>
+        <v>87.8</v>
       </c>
       <c r="P22">
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>89.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="R22">
-        <v>94.5</v>
+        <v>72.7</v>
       </c>
       <c r="S22">
-        <v>81.59999999999999</v>
+        <v>88.2</v>
       </c>
     </row>
   </sheetData>
@@ -3460,7 +3454,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>43</v>
@@ -3469,19 +3463,19 @@
         <v>19</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>57.9</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="G2" s="2">
-        <v>42.1</v>
+        <v>31.6</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3492,7 +3486,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>44</v>
@@ -3501,19 +3495,19 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>57.9</v>
+        <v>84.2</v>
       </c>
       <c r="G3" s="2">
-        <v>42.1</v>
+        <v>15.8</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3524,7 +3518,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>45</v>
@@ -3533,19 +3527,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>78.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="G4" s="2">
-        <v>21.1</v>
+        <v>15.8</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3556,7 +3550,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>46</v>
@@ -3565,16 +3559,16 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>84.2</v>
+        <v>89.5</v>
       </c>
       <c r="G5" s="2">
-        <v>15.8</v>
+        <v>10.5</v>
       </c>
       <c r="H5">
         <v>7.1</v>
@@ -3588,7 +3582,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>47</v>
@@ -3609,7 +3603,7 @@
         <v>10.5</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3641,7 +3635,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3723,22 +3717,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920322</v>
+        <v>20330051920317</v>
       </c>
       <c r="B2" t="s">
         <v>53</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -3746,19 +3740,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920397</v>
+        <v>20330051920317</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>44</v>
@@ -3769,22 +3763,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920326</v>
+        <v>20330051920397</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -3792,19 +3786,19 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920396</v>
+        <v>20330051920326</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
         <v>60</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>43</v>
@@ -3815,19 +3809,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920331</v>
+        <v>20330051920329</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
         <v>43</v>
@@ -3838,19 +3832,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920333</v>
+        <v>19330051920408</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
